--- a/artfynd/A 29320-2026 artfynd.xlsx
+++ b/artfynd/A 29320-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -809,6 +814,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115538423</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -940,6 +950,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485811</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1071,6 +1086,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128486080</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1202,6 +1222,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128643477</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1333,6 +1358,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132288055</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1464,6 +1494,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132288326</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1595,6 +1630,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132378180</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1726,6 +1766,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132441243</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1857,6 +1902,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132554603</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1988,6 +2038,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132554754</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2119,6 +2174,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132626416</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2245,6 +2305,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124295367</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2371,6 +2436,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127146583</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2497,6 +2567,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127937530</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2623,6 +2698,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128202848</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2749,6 +2829,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132463713</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2886,6 +2971,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122968537</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3028,6 +3118,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115538367</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3154,6 +3249,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127752094</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3280,6 +3380,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127772505</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3411,6 +3516,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128335394</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3542,6 +3652,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128352588</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3673,6 +3788,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128429347</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3804,6 +3924,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128485895</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3935,6 +4060,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128536947</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4068,6 +4198,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128609972</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4201,6 +4336,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131559407</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4334,6 +4474,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131594198</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4467,6 +4612,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131594284</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4600,6 +4750,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131682802</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4731,6 +4886,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131724573</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4862,6 +5022,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131756849</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4995,6 +5160,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131843901</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5126,6 +5296,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131946905</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5257,6 +5432,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131946969</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5388,6 +5568,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131947112</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5519,6 +5704,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132062948</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5650,6 +5840,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132084479</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5781,6 +5976,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132287989</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5912,6 +6112,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132315577</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6043,6 +6248,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132441041</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6174,6 +6384,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132441132</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6305,6 +6520,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132463616</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6436,6 +6656,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132490522</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6567,6 +6792,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132490571</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6698,8 +6928,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132520488</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 29320-2026 artfynd.xlsx
+++ b/artfynd/A 29320-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ47"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6931,6 +6931,142 @@
       <c r="AZ47" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132520488</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135760499</v>
+      </c>
+      <c r="B48" t="n">
+        <v>56930</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Tobokrysset, Tobokrysset, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>648896</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6680771</v>
+      </c>
+      <c r="S48" t="n">
+        <v>1</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Tierp</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Vendel</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anders Wahlström</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anders Wahlström</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135760499</t>
         </is>
       </c>
     </row>
@@ -6982,6 +7118,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29320-2026 artfynd.xlsx
+++ b/artfynd/A 29320-2026 artfynd.xlsx
@@ -6939,7 +6939,7 @@
         <v>135760499</v>
       </c>
       <c r="B48" t="n">
-        <v>56930</v>
+        <v>56932</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 29320-2026 artfynd.xlsx
+++ b/artfynd/A 29320-2026 artfynd.xlsx
@@ -6939,7 +6939,7 @@
         <v>135760499</v>
       </c>
       <c r="B48" t="n">
-        <v>56932</v>
+        <v>56933</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 29320-2026 artfynd.xlsx
+++ b/artfynd/A 29320-2026 artfynd.xlsx
@@ -6939,7 +6939,7 @@
         <v>135760499</v>
       </c>
       <c r="B48" t="n">
-        <v>56933</v>
+        <v>56937</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 29320-2026 artfynd.xlsx
+++ b/artfynd/A 29320-2026 artfynd.xlsx
@@ -6939,7 +6939,7 @@
         <v>135760499</v>
       </c>
       <c r="B48" t="n">
-        <v>56937</v>
+        <v>56938</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
